--- a/AAAGameData/Languages/Japanese.xlsx
+++ b/AAAGameData/Languages/Japanese.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>BRAKE</t>
   </si>
@@ -80,12 +80,15 @@
     <t>Failed</t>
   </si>
   <si>
-    <t/>
+    <t>ゲームに失敗しました</t>
   </si>
   <si>
     <t>GameOverUIForm.Back</t>
   </si>
   <si>
+    <t>戻る</t>
+  </si>
+  <si>
     <t>Level.DisplayName1</t>
   </si>
   <si>
@@ -243,6 +246,9 @@
   </si>
   <si>
     <t>Victory</t>
+  </si>
+  <si>
+    <t>ゲームに勝利</t>
   </si>
 </sst>
 </file>
@@ -424,6 +430,502 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
     <mc:Fallback/>
@@ -3997,250 +4499,250 @@
         <v>6</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1"/>
       <c r="B6" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1"/>
       <c r="B7" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1"/>
       <c r="B8" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1"/>
       <c r="B9" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1"/>
       <c r="B10" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1"/>
       <c r="B11" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1"/>
       <c r="B12" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1"/>
       <c r="B13" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1"/>
       <c r="B14" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1"/>
       <c r="B15" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1"/>
       <c r="B16" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1"/>
       <c r="B17" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1"/>
       <c r="B18" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1"/>
       <c r="B19" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1"/>
       <c r="B20" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1"/>
       <c r="B21" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1"/>
       <c r="B22" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1"/>
       <c r="B23" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1"/>
       <c r="B24" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1"/>
       <c r="B25" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1"/>
       <c r="B26" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1"/>
       <c r="B27" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1"/>
       <c r="B28" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1"/>
       <c r="B29" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1"/>
       <c r="B30" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1"/>
       <c r="B31" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -4255,7 +4757,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId150" name="A1">
+            <control shapeId="1056" r:id="rId270" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4277,7 +4779,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId151" name="A2">
+            <control shapeId="1057" r:id="rId271" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4299,7 +4801,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId152" name="A3">
+            <control shapeId="1058" r:id="rId272" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4321,7 +4823,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId153" name="A4">
+            <control shapeId="1059" r:id="rId273" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4343,7 +4845,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId154" name="A5">
+            <control shapeId="1060" r:id="rId274" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4365,7 +4867,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId155" name="A6">
+            <control shapeId="1061" r:id="rId275" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4387,7 +4889,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId156" name="A7">
+            <control shapeId="1062" r:id="rId276" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4409,7 +4911,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId157" name="A8">
+            <control shapeId="1063" r:id="rId277" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4431,7 +4933,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId158" name="A9">
+            <control shapeId="1064" r:id="rId278" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4453,7 +4955,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId159" name="A10">
+            <control shapeId="1065" r:id="rId279" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4475,7 +4977,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId160" name="A11">
+            <control shapeId="1066" r:id="rId280" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4497,7 +4999,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId161" name="A12">
+            <control shapeId="1067" r:id="rId281" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4519,7 +5021,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId162" name="A13">
+            <control shapeId="1068" r:id="rId282" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4541,7 +5043,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId163" name="A14">
+            <control shapeId="1069" r:id="rId283" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4563,7 +5065,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId164" name="A15">
+            <control shapeId="1070" r:id="rId284" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4585,7 +5087,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId165" name="A16">
+            <control shapeId="1071" r:id="rId285" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4607,7 +5109,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId166" name="A17">
+            <control shapeId="1072" r:id="rId286" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4629,7 +5131,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId167" name="A18">
+            <control shapeId="1073" r:id="rId287" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4651,7 +5153,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId168" name="A19">
+            <control shapeId="1074" r:id="rId288" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4673,7 +5175,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId169" name="A20">
+            <control shapeId="1075" r:id="rId289" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4695,7 +5197,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId170" name="A21">
+            <control shapeId="1076" r:id="rId290" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4717,7 +5219,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId171" name="A22">
+            <control shapeId="1077" r:id="rId291" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4739,7 +5241,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId172" name="A23">
+            <control shapeId="1078" r:id="rId292" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4761,7 +5263,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId173" name="A24">
+            <control shapeId="1079" r:id="rId293" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4783,7 +5285,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId174" name="A25">
+            <control shapeId="1080" r:id="rId294" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4805,7 +5307,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId175" name="A26">
+            <control shapeId="1081" r:id="rId295" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4827,7 +5329,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId176" name="A27">
+            <control shapeId="1082" r:id="rId296" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4849,7 +5351,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId177" name="A28">
+            <control shapeId="1083" r:id="rId297" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4871,7 +5373,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId178" name="A29">
+            <control shapeId="1084" r:id="rId298" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4893,7 +5395,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId179" name="A30">
+            <control shapeId="1085" r:id="rId299" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4915,7 +5417,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId180" name="A31">
+            <control shapeId="1086" r:id="rId300" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>

--- a/AAAGameData/Languages/Japanese.xlsx
+++ b/AAAGameData/Languages/Japanese.xlsx
@@ -63,12 +63,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>NoSaveData</t>
   </si>
   <si>
-    <t/>
+    <t>アーカイブデータがありません</t>
   </si>
   <si>
     <t>Nothing</t>
@@ -95,6 +95,30 @@
     <t>保存リストを開く</t>
   </si>
   <si>
+    <t>scene.base.name</t>
+  </si>
+  <si>
+    <t>きち</t>
+  </si>
+  <si>
+    <t>scene.menu.name</t>
+  </si>
+  <si>
+    <t>メインメニュー</t>
+  </si>
+  <si>
+    <t>scene.tutorial.name</t>
+  </si>
+  <si>
+    <t>ある実験室</t>
+  </si>
+  <si>
+    <t>scene.world.name</t>
+  </si>
+  <si>
+    <t>大世界</t>
+  </si>
+  <si>
     <t>Settings.Help</t>
   </si>
   <si>
@@ -116,7 +140,7 @@
     <t>Settings.Privacy</t>
   </si>
   <si>
-    <t>プライバシーポリシー</t>
+    <t>プライバシー契約</t>
   </si>
   <si>
     <t>Settings.Rating</t>
@@ -152,7 +176,7 @@
     <t>TermsOfService</t>
   </si>
   <si>
-    <t>サービス条件</t>
+    <t>利用規約</t>
   </si>
   <si>
     <t>UI_Continue</t>
@@ -176,7 +200,7 @@
     <t>UI_Welcome</t>
   </si>
   <si>
-    <t>ようこそ、！</t>
+    <t>ようこそ</t>
   </si>
 </sst>
 </file>
@@ -253,7 +277,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
@@ -261,7 +285,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
@@ -277,6 +301,22 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -2195,6 +2235,634 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -2211,351 +2879,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1044">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1044"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1045">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1045"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1046">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1046"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1047">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1047"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1048">
+            <xdr:cNvPr hidden="1" name="A1" id="1048">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1048"/>
@@ -2630,18 +2954,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1049">
+            <xdr:cNvPr hidden="1" name="A2" id="1049">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1049"/>
@@ -2716,18 +3040,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1050">
+            <xdr:cNvPr hidden="1" name="A3" id="1050">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1050"/>
@@ -2802,18 +3126,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1051">
+            <xdr:cNvPr hidden="1" name="A4" id="1051">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1051"/>
@@ -2888,18 +3212,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1052">
+            <xdr:cNvPr hidden="1" name="A5" id="1052">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1052"/>
@@ -2974,18 +3298,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1053">
+            <xdr:cNvPr hidden="1" name="A6" id="1053">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1053"/>
@@ -3060,18 +3384,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1054">
+            <xdr:cNvPr hidden="1" name="A7" id="1054">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1054"/>
@@ -3146,18 +3470,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1055">
+            <xdr:cNvPr hidden="1" name="A8" id="1055">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1055"/>
@@ -3232,18 +3556,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1056">
+            <xdr:cNvPr hidden="1" name="A9" id="1056">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1056"/>
@@ -3318,18 +3642,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1057">
+            <xdr:cNvPr hidden="1" name="A10" id="1057">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1057"/>
@@ -3404,18 +3728,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1058">
+            <xdr:cNvPr hidden="1" name="A11" id="1058">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1058"/>
@@ -3490,18 +3814,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1059">
+            <xdr:cNvPr hidden="1" name="A12" id="1059">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1059"/>
@@ -3576,18 +3900,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1060">
+            <xdr:cNvPr hidden="1" name="A13" id="1060">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1060"/>
@@ -3662,18 +3986,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1061">
+            <xdr:cNvPr hidden="1" name="A14" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1061"/>
@@ -3748,6 +4072,350 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A15" id="1062">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1062"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A16" id="1063">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1063"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A17" id="1064">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1064"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A18" id="1065">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1065"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -3759,10 +4427,354 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1062">
+            <xdr:cNvPr hidden="1" name="A19" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1062"/>
+                  <a14:compatExt spid="_x0000_s1066"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A20" id="1067">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1067"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A21" id="1068">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1068"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A22" id="1069">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1069"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A23" id="1070">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1070"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4094,7 +5106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -4273,6 +5285,42 @@
         <v>37</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="1"/>
+      <c r="B20" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1"/>
+      <c r="B21" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1"/>
+      <c r="B22" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1"/>
+      <c r="B23" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4285,7 +5333,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1044" r:id="rId456" name="A1">
+            <control shapeId="1048" r:id="rId606" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4307,7 +5355,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1045" r:id="rId457" name="A2">
+            <control shapeId="1049" r:id="rId607" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4329,7 +5377,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1046" r:id="rId458" name="A3">
+            <control shapeId="1050" r:id="rId608" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4351,7 +5399,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1047" r:id="rId459" name="A4">
+            <control shapeId="1051" r:id="rId609" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4373,7 +5421,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1048" r:id="rId460" name="A5">
+            <control shapeId="1052" r:id="rId610" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4395,7 +5443,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1049" r:id="rId461" name="A6">
+            <control shapeId="1053" r:id="rId611" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4417,7 +5465,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1050" r:id="rId462" name="A7">
+            <control shapeId="1054" r:id="rId612" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4439,7 +5487,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1051" r:id="rId463" name="A8">
+            <control shapeId="1055" r:id="rId613" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4461,7 +5509,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1052" r:id="rId464" name="A9">
+            <control shapeId="1056" r:id="rId614" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4483,7 +5531,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1053" r:id="rId465" name="A10">
+            <control shapeId="1057" r:id="rId615" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4505,7 +5553,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1054" r:id="rId466" name="A11">
+            <control shapeId="1058" r:id="rId616" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4527,7 +5575,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1055" r:id="rId467" name="A12">
+            <control shapeId="1059" r:id="rId617" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4549,7 +5597,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId468" name="A13">
+            <control shapeId="1060" r:id="rId618" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4571,7 +5619,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId469" name="A14">
+            <control shapeId="1061" r:id="rId619" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4593,7 +5641,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId470" name="A15">
+            <control shapeId="1062" r:id="rId620" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4615,7 +5663,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId471" name="A16">
+            <control shapeId="1063" r:id="rId621" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4637,7 +5685,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId472" name="A17">
+            <control shapeId="1064" r:id="rId622" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4659,7 +5707,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId473" name="A18">
+            <control shapeId="1065" r:id="rId623" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4681,7 +5729,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId474" name="A19">
+            <control shapeId="1066" r:id="rId624" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4701,6 +5749,94 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1067" r:id="rId625" name="A20">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1068" r:id="rId626" name="A21">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1069" r:id="rId627" name="A22">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1070" r:id="rId628" name="A23">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>

--- a/AAAGameData/Languages/Japanese.xlsx
+++ b/AAAGameData/Languages/Japanese.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>NoSaveData</t>
   </si>
@@ -95,16 +95,58 @@
     <t>保存リストを開く</t>
   </si>
   <si>
+    <t>scene.abyss.name</t>
+  </si>
+  <si>
+    <t>深淵の地</t>
+  </si>
+  <si>
+    <t>scene.avalon.name</t>
+  </si>
+  <si>
+    <t>アバロン</t>
+  </si>
+  <si>
+    <t>scene.babylon.name</t>
+  </si>
+  <si>
+    <t>バビロン空中庭園</t>
+  </si>
+  <si>
     <t>scene.base.name</t>
   </si>
   <si>
     <t>きち</t>
   </si>
   <si>
+    <t>scene.herheim.name</t>
+  </si>
+  <si>
+    <t>ハルハイマー</t>
+  </si>
+  <si>
     <t>scene.menu.name</t>
   </si>
   <si>
     <t>メインメニュー</t>
+  </si>
+  <si>
+    <t>scene.olympus.name</t>
+  </si>
+  <si>
+    <t>オリンポス山</t>
+  </si>
+  <si>
+    <t>scene.takamahara.name</t>
+  </si>
+  <si>
+    <t>高天原</t>
+  </si>
+  <si>
+    <t>scene.tiangong.name</t>
+  </si>
+  <si>
+    <t>天宮（てんぐう）</t>
   </si>
   <si>
     <t>scene.tutorial.name</t>
@@ -261,7 +303,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
@@ -269,15 +311,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
@@ -293,7 +335,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
@@ -305,7 +347,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
@@ -313,14 +355,42 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -333,15 +403,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
@@ -350,6 +420,338 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
     <mc:Fallback/>
@@ -2879,609 +3281,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1048">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1048"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1049">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1049"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1050">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1050"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1051">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1051"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1052">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1052"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1053">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1053"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1054">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1054"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1055">
+            <xdr:cNvPr hidden="1" name="A1" id="1055">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1055"/>
@@ -3556,18 +3356,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1056">
+            <xdr:cNvPr hidden="1" name="A2" id="1056">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1056"/>
@@ -3642,18 +3442,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1057">
+            <xdr:cNvPr hidden="1" name="A3" id="1057">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1057"/>
@@ -3728,18 +3528,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1058">
+            <xdr:cNvPr hidden="1" name="A4" id="1058">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1058"/>
@@ -3814,18 +3614,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1059">
+            <xdr:cNvPr hidden="1" name="A5" id="1059">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1059"/>
@@ -3900,18 +3700,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1060">
+            <xdr:cNvPr hidden="1" name="A6" id="1060">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1060"/>
@@ -3986,18 +3786,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1061">
+            <xdr:cNvPr hidden="1" name="A7" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1061"/>
@@ -4072,18 +3872,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1062">
+            <xdr:cNvPr hidden="1" name="A8" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1062"/>
@@ -4158,18 +3958,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1063">
+            <xdr:cNvPr hidden="1" name="A9" id="1063">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1063"/>
@@ -4244,18 +4044,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1064">
+            <xdr:cNvPr hidden="1" name="A10" id="1064">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1064"/>
@@ -4330,18 +4130,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1065">
+            <xdr:cNvPr hidden="1" name="A11" id="1065">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1065"/>
@@ -4416,18 +4216,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1066">
+            <xdr:cNvPr hidden="1" name="A12" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1066"/>
@@ -4502,18 +4302,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1067">
+            <xdr:cNvPr hidden="1" name="A13" id="1067">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1067"/>
@@ -4588,18 +4388,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1068">
+            <xdr:cNvPr hidden="1" name="A14" id="1068">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1068"/>
@@ -4674,18 +4474,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1069">
+            <xdr:cNvPr hidden="1" name="A15" id="1069">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1069"/>
@@ -4760,6 +4560,608 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A16" id="1070">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1070"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A17" id="1071">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1071"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A18" id="1072">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1072"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A19" id="1073">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1073"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A20" id="1074">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1074"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A21" id="1075">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1075"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A22" id="1076">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1076"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -4771,10 +5173,612 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1070">
+            <xdr:cNvPr hidden="1" name="A23" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1070"/>
+                  <a14:compatExt spid="_x0000_s1077"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A24" id="1078">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1078"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A25" id="1079">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1079"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A26" id="1080">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1080"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A27" id="1081">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1081"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A28" id="1082">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1082"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A29" id="1083">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1083"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>30</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A30" id="1084">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1084"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5106,11 +6110,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22.2728118896484" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5321,6 +6325,69 @@
         <v>45</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="1"/>
+      <c r="B24" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1"/>
+      <c r="B26" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1"/>
+      <c r="B27" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1"/>
+      <c r="B28" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1"/>
+      <c r="B29" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1"/>
+      <c r="B30" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5333,7 +6400,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1048" r:id="rId606" name="A1">
+            <control shapeId="1055" r:id="rId686" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5355,7 +6422,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1049" r:id="rId607" name="A2">
+            <control shapeId="1056" r:id="rId687" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5377,7 +6444,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1050" r:id="rId608" name="A3">
+            <control shapeId="1057" r:id="rId688" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5399,7 +6466,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1051" r:id="rId609" name="A4">
+            <control shapeId="1058" r:id="rId689" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5421,7 +6488,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1052" r:id="rId610" name="A5">
+            <control shapeId="1059" r:id="rId690" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5443,7 +6510,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1053" r:id="rId611" name="A6">
+            <control shapeId="1060" r:id="rId691" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5465,7 +6532,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1054" r:id="rId612" name="A7">
+            <control shapeId="1061" r:id="rId692" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5487,7 +6554,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1055" r:id="rId613" name="A8">
+            <control shapeId="1062" r:id="rId693" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5509,7 +6576,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId614" name="A9">
+            <control shapeId="1063" r:id="rId694" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5531,7 +6598,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId615" name="A10">
+            <control shapeId="1064" r:id="rId695" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5553,7 +6620,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId616" name="A11">
+            <control shapeId="1065" r:id="rId696" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5575,7 +6642,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId617" name="A12">
+            <control shapeId="1066" r:id="rId697" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5597,7 +6664,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId618" name="A13">
+            <control shapeId="1067" r:id="rId698" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5619,7 +6686,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId619" name="A14">
+            <control shapeId="1068" r:id="rId699" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5641,7 +6708,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId620" name="A15">
+            <control shapeId="1069" r:id="rId700" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5663,7 +6730,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId621" name="A16">
+            <control shapeId="1070" r:id="rId701" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5685,7 +6752,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId622" name="A17">
+            <control shapeId="1071" r:id="rId702" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5707,7 +6774,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId623" name="A18">
+            <control shapeId="1072" r:id="rId703" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5729,7 +6796,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId624" name="A19">
+            <control shapeId="1073" r:id="rId704" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5751,7 +6818,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId625" name="A20">
+            <control shapeId="1074" r:id="rId705" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5773,7 +6840,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId626" name="A21">
+            <control shapeId="1075" r:id="rId706" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5795,7 +6862,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId627" name="A22">
+            <control shapeId="1076" r:id="rId707" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5817,7 +6884,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId628" name="A23">
+            <control shapeId="1077" r:id="rId708" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5837,6 +6904,160 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1078" r:id="rId709" name="A24">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>24</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1079" r:id="rId710" name="A25">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>24</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1080" r:id="rId711" name="A26">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1081" r:id="rId712" name="A27">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1082" r:id="rId713" name="A28">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1083" r:id="rId714" name="A29">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1084" r:id="rId715" name="A30">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>30</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>
